--- a/data/nzd0169/nzd0169.xlsx
+++ b/data/nzd0169/nzd0169.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E597"/>
+  <dimension ref="A1:E602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12969,6 +12969,111 @@
         <v>367.01</v>
       </c>
       <c r="E597" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B598" t="n">
+        <v>374.26</v>
+      </c>
+      <c r="C598" t="n">
+        <v>366.54</v>
+      </c>
+      <c r="D598" t="n">
+        <v>367.61</v>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B599" t="n">
+        <v>373.96</v>
+      </c>
+      <c r="C599" t="n">
+        <v>366.49</v>
+      </c>
+      <c r="D599" t="n">
+        <v>367.02</v>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B600" t="n">
+        <v>373.76</v>
+      </c>
+      <c r="C600" t="n">
+        <v>366.52</v>
+      </c>
+      <c r="D600" t="n">
+        <v>367.05</v>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="n">
+        <v>373.76</v>
+      </c>
+      <c r="C601" t="n">
+        <v>366.52</v>
+      </c>
+      <c r="D601" t="n">
+        <v>367.18</v>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B602" t="n">
+        <v>373.65</v>
+      </c>
+      <c r="C602" t="n">
+        <v>366.54</v>
+      </c>
+      <c r="D602" t="n">
+        <v>367.36</v>
+      </c>
+      <c r="E602" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12985,7 +13090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B691"/>
+  <dimension ref="A1:B696"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19898,6 +20003,56 @@
       </c>
       <c r="B691" t="n">
         <v>-0.9</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="n">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="n">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="n">
+        <v>-0.3</v>
       </c>
     </row>
   </sheetData>
@@ -20066,28 +20221,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01845431048539821</v>
+        <v>-0.02009670845341464</v>
       </c>
       <c r="J2" t="n">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="K2" t="n">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002329634248521284</v>
+        <v>0.002806495661840991</v>
       </c>
       <c r="M2" t="n">
-        <v>2.245558808483953</v>
+        <v>2.234623669960337</v>
       </c>
       <c r="N2" t="n">
-        <v>8.518046176648372</v>
+        <v>8.456671366916032</v>
       </c>
       <c r="O2" t="n">
-        <v>2.918569200250077</v>
+        <v>2.908035654340578</v>
       </c>
       <c r="P2" t="n">
-        <v>375.433906202712</v>
+        <v>375.4512033238909</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20144,28 +20299,28 @@
         <v>0.096</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07879779676199966</v>
+        <v>-0.07723173703131428</v>
       </c>
       <c r="J3" t="n">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="K3" t="n">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07518403216089897</v>
+        <v>0.07348391376256724</v>
       </c>
       <c r="M3" t="n">
-        <v>1.658521846192087</v>
+        <v>1.653234624315096</v>
       </c>
       <c r="N3" t="n">
-        <v>4.460698488011341</v>
+        <v>4.431867977223409</v>
       </c>
       <c r="O3" t="n">
-        <v>2.112036573549649</v>
+        <v>2.105200222597226</v>
       </c>
       <c r="P3" t="n">
-        <v>367.6321971948114</v>
+        <v>367.6157069033058</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20222,28 +20377,28 @@
         <v>0.0915</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.08143298724520188</v>
+        <v>-0.0800875736243091</v>
       </c>
       <c r="J4" t="n">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="K4" t="n">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06566902760784055</v>
+        <v>0.06462168100746002</v>
       </c>
       <c r="M4" t="n">
-        <v>1.918804774314182</v>
+        <v>1.91036246485727</v>
       </c>
       <c r="N4" t="n">
-        <v>5.510435291749848</v>
+        <v>5.471089816918423</v>
       </c>
       <c r="O4" t="n">
-        <v>2.347431637289966</v>
+        <v>2.339036087134703</v>
       </c>
       <c r="P4" t="n">
-        <v>368.5662737760064</v>
+        <v>368.5521066970734</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20281,7 +20436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E597"/>
+  <dimension ref="A1:E602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36403,6 +36558,141 @@
         </is>
       </c>
     </row>
+    <row r="598">
+      <c r="A598" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>-36.7707873372621,174.77314498420844</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>-36.77138368311541,174.7736432355447</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>-36.77194858661096,174.77419420144167</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>-36.77078897447925,174.7731423098745</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>-36.7713839662829,174.77364279985665</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>-36.77195185125919,174.77418898467621</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>-36.770790065957314,174.77314052698512</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>-36.771383796382416,174.7736430612695</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>-36.771951685260134,174.7741892499355</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>-36.770790065957314,174.77314052698512</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>-36.771383796382416,174.7736430612695</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>-36.77195096593088,174.7741903993923</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>-36.770790666270265,174.77313954639595</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>-36.77138368311541,174.7736432355447</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>-36.771949969936514,174.77419199094786</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0169/nzd0169.xlsx
+++ b/data/nzd0169/nzd0169.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E602"/>
+  <dimension ref="A1:E606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13074,6 +13074,90 @@
         <v>367.36</v>
       </c>
       <c r="E602" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B603" t="n">
+        <v>373.84</v>
+      </c>
+      <c r="C603" t="n">
+        <v>366.69</v>
+      </c>
+      <c r="D603" t="n">
+        <v>367.87</v>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B604" t="n">
+        <v>374.15</v>
+      </c>
+      <c r="C604" t="n">
+        <v>366.93</v>
+      </c>
+      <c r="D604" t="n">
+        <v>368.23</v>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B605" t="n">
+        <v>374.17</v>
+      </c>
+      <c r="C605" t="n">
+        <v>366.78</v>
+      </c>
+      <c r="D605" t="n">
+        <v>368.49</v>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B606" t="n">
+        <v>373.86</v>
+      </c>
+      <c r="C606" t="n">
+        <v>366.48</v>
+      </c>
+      <c r="D606" t="n">
+        <v>368.52</v>
+      </c>
+      <c r="E606" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13090,7 +13174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B696"/>
+  <dimension ref="A1:B700"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20053,6 +20137,46 @@
       </c>
       <c r="B696" t="n">
         <v>-0.3</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B697" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B698" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B699" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B700" t="n">
+        <v>0.58</v>
       </c>
     </row>
   </sheetData>
@@ -20221,28 +20345,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02009670845341464</v>
+        <v>-0.02120316295398662</v>
       </c>
       <c r="J2" t="n">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="K2" t="n">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002806495661840991</v>
+        <v>0.003163819824745229</v>
       </c>
       <c r="M2" t="n">
-        <v>2.234623669960337</v>
+        <v>2.225006666087837</v>
       </c>
       <c r="N2" t="n">
-        <v>8.456671366916032</v>
+        <v>8.406200179974702</v>
       </c>
       <c r="O2" t="n">
-        <v>2.908035654340578</v>
+        <v>2.899344784597841</v>
       </c>
       <c r="P2" t="n">
-        <v>375.4512033238909</v>
+        <v>375.46290405556</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20299,28 +20423,28 @@
         <v>0.096</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07723173703131428</v>
+        <v>-0.07577788622595054</v>
       </c>
       <c r="J3" t="n">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="K3" t="n">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07348391376256724</v>
+        <v>0.07170287589143631</v>
       </c>
       <c r="M3" t="n">
-        <v>1.653234624315096</v>
+        <v>1.650111697538067</v>
       </c>
       <c r="N3" t="n">
-        <v>4.431867977223409</v>
+        <v>4.41186058232204</v>
       </c>
       <c r="O3" t="n">
-        <v>2.105200222597226</v>
+        <v>2.100442949075751</v>
       </c>
       <c r="P3" t="n">
-        <v>367.6157069033058</v>
+        <v>367.6003348599514</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20377,28 +20501,28 @@
         <v>0.0915</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0800875736243091</v>
+        <v>-0.07777656572253018</v>
       </c>
       <c r="J4" t="n">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="K4" t="n">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06462168100746002</v>
+        <v>0.06171001156918043</v>
       </c>
       <c r="M4" t="n">
-        <v>1.91036246485727</v>
+        <v>1.910644728723335</v>
       </c>
       <c r="N4" t="n">
-        <v>5.471089816918423</v>
+        <v>5.458399975340584</v>
       </c>
       <c r="O4" t="n">
-        <v>2.339036087134703</v>
+        <v>2.336321890352565</v>
       </c>
       <c r="P4" t="n">
-        <v>368.5521066970734</v>
+        <v>368.5276646577993</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20436,7 +20560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E602"/>
+  <dimension ref="A1:E606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36693,6 +36817,114 @@
         </is>
       </c>
     </row>
+    <row r="603">
+      <c r="A603" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>-36.7707896293661,174.7731412401409</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>-36.77138283361296,174.77364454260882</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>-36.77194714795234,174.7741965003551</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>-36.77078793757505,174.77314400361936</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>-36.771381474408976,174.77364663391137</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>-36.77194515596343,174.77419968346587</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>-36.77078782842725,174.77314418190826</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>-36.77138232391146,174.7736453268473</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>-36.77194371730472,174.7742019823791</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>-36.770789520218294,174.77314141842982</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>-36.7713840229164,174.77364271271904</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>-36.77194355130564,174.77420224763833</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
